--- a/synuclein_inclusion_biogenesis_2024/image_analysis/linoleic_acid/72325_SUMMARY.xlsx
+++ b/synuclein_inclusion_biogenesis_2024/image_analysis/linoleic_acid/72325_SUMMARY.xlsx
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1032</v>
+        <v>1110</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -651,16 +651,16 @@
         <v>23879</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -697,16 +697,16 @@
         <v>14961</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -743,16 +743,16 @@
         <v>33141</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>540</v>
+        <v>448</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -844,7 +844,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>273.5</v>
+        <v>333</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>513.5</v>
+        <v>574</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>834.6666666666666</v>
+        <v>881.3333333333334</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -1626,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>281.6666666666667</v>
+        <v>325</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -1939,16 +1939,16 @@
         <v>12423</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>774</v>
+        <v>823</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>415</v>
+        <v>522</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>222</v>
+        <v>279</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>575</v>
+        <v>636</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>575</v>
+        <v>636</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>762</v>
+        <v>825</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2859,16 +2859,16 @@
         <v>15002</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>432</v>
+        <v>244</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2905,16 +2905,16 @@
         <v>11983</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>174.5</v>
+        <v>159.3333333333333</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>427.5</v>
+        <v>524.5</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3696,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>539</v>
+        <v>613</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>540</v>
+        <v>614</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>25618</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
         <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>784.6666666666666</v>
+        <v>660.5</v>
       </c>
       <c r="H73" t="n">
         <v>3</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>464</v>
+        <v>526</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>845</v>
+        <v>944</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4147,16 +4147,16 @@
         <v>15745</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
         <v>30981</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>739.5</v>
+        <v>530</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>3</v>
@@ -4340,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>362</v>
+        <v>432</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>1392</v>
+        <v>1513</v>
       </c>
       <c r="H90" t="n">
         <v>2</v>
@@ -4754,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>461.5</v>
+        <v>581.5</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4791,16 +4791,16 @@
         <v>15442</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4846,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>627.5</v>
+        <v>620</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>654.5</v>
+        <v>721.5</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="H99" t="n">
         <v>2</v>
@@ -5021,16 +5021,16 @@
         <v>11534</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>615</v>
+        <v>301</v>
       </c>
       <c r="H100" t="n">
         <v>1</v>
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>719</v>
+        <v>687</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -5159,16 +5159,16 @@
         <v>15155</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -5260,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>14233</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>266</v>
+        <v>224.5</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
@@ -5364,10 +5364,10 @@
         <v>3</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="H110" t="n">
         <v>1</v>
@@ -5812,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>1022</v>
+        <v>1136</v>
       </c>
       <c r="H117" t="n">
         <v>2</v>
@@ -5904,7 +5904,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -6079,22 +6079,22 @@
         <v>11943</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>857</v>
+        <v>507.5</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>1</v>
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>1047</v>
+        <v>1189</v>
       </c>
       <c r="H131" t="n">
         <v>4</v>
@@ -6502,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>419</v>
+        <v>505</v>
       </c>
       <c r="H132" t="n">
         <v>1</v>
@@ -6594,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6686,7 +6686,7 @@
         <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="H136" t="n">
         <v>1</v>
@@ -6870,7 +6870,7 @@
         <v>1</v>
       </c>
       <c r="G140" t="n">
-        <v>86</v>
+        <v>162.5</v>
       </c>
       <c r="H140" t="n">
         <v>1</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>658</v>
+        <v>787</v>
       </c>
       <c r="H141" t="n">
         <v>2</v>
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>787</v>
+        <v>993</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>1313</v>
+        <v>1542</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7468,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>787</v>
+        <v>993</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>861.5</v>
+        <v>1089</v>
       </c>
       <c r="H168" t="n">
         <v>2</v>
@@ -8195,22 +8195,22 @@
         <v>16428</v>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>1118</v>
+        <v>761.5</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J169" t="n">
         <v>8</v>
@@ -8388,7 +8388,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>963</v>
+        <v>1235</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -8425,16 +8425,16 @@
         <v>2928</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>1</v>
       </c>
       <c r="G175" t="n">
-        <v>88</v>
+        <v>263</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
         <v>1</v>
       </c>
       <c r="G176" t="n">
-        <v>492.5</v>
+        <v>585</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8572,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="H177" t="n">
         <v>1</v>
@@ -8710,7 +8710,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>298</v>
+        <v>387</v>
       </c>
       <c r="H180" t="n">
         <v>1</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>173</v>
+        <v>294</v>
       </c>
       <c r="H184" t="n">
         <v>1</v>
@@ -8931,16 +8931,16 @@
         <v>40401</v>
       </c>
       <c r="D185" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E185" t="n">
         <v>3</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G185" t="n">
-        <v>445</v>
+        <v>323.8333333333333</v>
       </c>
       <c r="H185" t="n">
         <v>4</v>
@@ -8977,16 +8977,16 @@
         <v>15852</v>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>173</v>
+        <v>171.5</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>265</v>
+        <v>358</v>
       </c>
       <c r="H187" t="n">
         <v>1</v>
@@ -9161,16 +9161,16 @@
         <v>23585</v>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G190" t="n">
-        <v>823</v>
+        <v>407</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -9216,13 +9216,13 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>199.3333333333333</v>
+        <v>298.3333333333333</v>
       </c>
       <c r="H191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I191" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J191" t="n">
         <v>10</v>
@@ -9253,16 +9253,16 @@
         <v>20505</v>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G192" t="n">
-        <v>44</v>
+        <v>103.6666666666667</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>174</v>
+        <v>243.5</v>
       </c>
       <c r="H197" t="n">
         <v>2</v>
@@ -9529,16 +9529,16 @@
         <v>20154</v>
       </c>
       <c r="D198" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E198" t="n">
         <v>2</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G198" t="n">
-        <v>182.3333333333333</v>
+        <v>154.4</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -9676,7 +9676,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="n">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9759,16 +9759,16 @@
         <v>27833</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G203" t="n">
-        <v>357</v>
+        <v>305</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9814,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>187</v>
+        <v>245</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9860,7 +9860,7 @@
         <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>357</v>
+        <v>489</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9989,16 +9989,16 @@
         <v>4006</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -10081,16 +10081,16 @@
         <v>21626</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G210" t="n">
-        <v>797</v>
+        <v>439</v>
       </c>
       <c r="H210" t="n">
         <v>2</v>
@@ -10219,16 +10219,16 @@
         <v>20301</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G213" t="n">
-        <v>525</v>
+        <v>350</v>
       </c>
       <c r="H213" t="n">
         <v>1</v>
@@ -10311,16 +10311,16 @@
         <v>30846</v>
       </c>
       <c r="D215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G215" t="n">
-        <v>183.3333333333333</v>
+        <v>252</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -10403,16 +10403,16 @@
         <v>23897</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>133.5</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -10449,22 +10449,22 @@
         <v>12087</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J218" t="n">
         <v>3</v>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
@@ -10633,16 +10633,16 @@
         <v>23314</v>
       </c>
       <c r="D222" t="n">
+        <v>7</v>
+      </c>
+      <c r="E222" t="n">
+        <v>2</v>
+      </c>
+      <c r="F222" t="n">
         <v>5</v>
       </c>
-      <c r="E222" t="n">
-        <v>2</v>
-      </c>
-      <c r="F222" t="n">
-        <v>3</v>
-      </c>
       <c r="G222" t="n">
-        <v>348.2</v>
+        <v>352.1428571428572</v>
       </c>
       <c r="H222" t="n">
         <v>3</v>
@@ -10679,16 +10679,16 @@
         <v>26379</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G223" t="n">
-        <v>46</v>
+        <v>104.5</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10725,16 +10725,16 @@
         <v>17003</v>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E224" t="n">
         <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G224" t="n">
-        <v>351</v>
+        <v>404.3333333333333</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10863,16 +10863,16 @@
         <v>24316</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" t="n">
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10918,7 +10918,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>470</v>
+        <v>599</v>
       </c>
       <c r="H228" t="n">
         <v>1</v>
@@ -11001,16 +11001,16 @@
         <v>18624</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
         <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -11047,16 +11047,16 @@
         <v>23556</v>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G231" t="n">
-        <v>73</v>
+        <v>120.25</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -11102,7 +11102,7 @@
         <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -11277,16 +11277,16 @@
         <v>38644</v>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" t="n">
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -11323,16 +11323,16 @@
         <v>16278</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E237" t="n">
         <v>1</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
-        <v>847</v>
+        <v>399.3333333333333</v>
       </c>
       <c r="H237" t="n">
         <v>1</v>
@@ -11369,16 +11369,16 @@
         <v>10881</v>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>21235</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G239" t="n">
-        <v>498</v>
+        <v>333.5</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -11461,22 +11461,22 @@
         <v>26605</v>
       </c>
       <c r="D240" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E240" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="H240" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J240" t="n">
         <v>8</v>
@@ -11562,7 +11562,7 @@
         <v>1</v>
       </c>
       <c r="G242" t="n">
-        <v>498</v>
+        <v>564</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -11838,7 +11838,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>935</v>
+        <v>1153</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11930,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11967,16 +11967,16 @@
         <v>32440</v>
       </c>
       <c r="D251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F251" t="n">
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>296</v>
+        <v>285.3333333333333</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11988,10 +11988,10 @@
         <v>1</v>
       </c>
       <c r="K251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M251" t="n">
         <v>4</v>
@@ -12013,16 +12013,16 @@
         <v>23527</v>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" t="n">
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -12059,16 +12059,16 @@
         <v>24206</v>
       </c>
       <c r="D253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F253" t="n">
         <v>1</v>
       </c>
       <c r="G253" t="n">
-        <v>775</v>
+        <v>501</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -12080,10 +12080,10 @@
         <v>5</v>
       </c>
       <c r="K253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
         <v>1</v>
@@ -12105,16 +12105,16 @@
         <v>14284</v>
       </c>
       <c r="D254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F254" t="n">
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>938</v>
+        <v>657.5</v>
       </c>
       <c r="H254" t="n">
         <v>2</v>
@@ -12126,10 +12126,10 @@
         <v>3</v>
       </c>
       <c r="K254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
         <v>2</v>
@@ -12344,7 +12344,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>336</v>
+        <v>463</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -12381,22 +12381,22 @@
         <v>18690</v>
       </c>
       <c r="D260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E260" t="n">
         <v>2</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
-        <v>277</v>
+        <v>302.6666666666667</v>
       </c>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I260" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J260" t="n">
         <v>6</v>
@@ -12574,7 +12574,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>369</v>
+        <v>437</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -12611,16 +12611,16 @@
         <v>9679</v>
       </c>
       <c r="D265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E265" t="n">
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -12657,16 +12657,16 @@
         <v>23184</v>
       </c>
       <c r="D266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E266" t="n">
         <v>2</v>
       </c>
       <c r="F266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G266" t="n">
-        <v>807.6666666666666</v>
+        <v>725</v>
       </c>
       <c r="H266" t="n">
         <v>2</v>
@@ -12712,7 +12712,7 @@
         <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -12749,16 +12749,16 @@
         <v>9536</v>
       </c>
       <c r="D268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E268" t="n">
         <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -12979,16 +12979,16 @@
         <v>3028</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -13034,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>1200</v>
+        <v>1321</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -13080,7 +13080,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="H275" t="n">
         <v>1</v>
@@ -13163,16 +13163,16 @@
         <v>22378</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E277" t="n">
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -13209,16 +13209,16 @@
         <v>24574</v>
       </c>
       <c r="D278" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E278" t="n">
         <v>3</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>578.3333333333334</v>
+        <v>497.5</v>
       </c>
       <c r="H278" t="n">
         <v>2</v>
@@ -13255,22 +13255,22 @@
         <v>19657</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>1153</v>
+        <v>924.6666666666666</v>
       </c>
       <c r="H279" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I279" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J279" t="n">
         <v>8</v>
@@ -13301,22 +13301,22 @@
         <v>33048</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" t="n">
         <v>1</v>
       </c>
       <c r="G280" t="n">
-        <v>14</v>
+        <v>125.5</v>
       </c>
       <c r="H280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="n">
         <v>3</v>
@@ -13402,7 +13402,7 @@
         <v>2</v>
       </c>
       <c r="G282" t="n">
-        <v>412.5</v>
+        <v>529.75</v>
       </c>
       <c r="H282" t="n">
         <v>3</v>
@@ -13448,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>358</v>
+        <v>425</v>
       </c>
       <c r="H283" t="n">
         <v>1</v>
@@ -13494,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>1666</v>
+        <v>1881</v>
       </c>
       <c r="H285" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -13761,16 +13761,16 @@
         <v>24736</v>
       </c>
       <c r="D290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
         <v>0</v>
       </c>
       <c r="F290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G290" t="n">
-        <v>309</v>
+        <v>204</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -13862,7 +13862,7 @@
         <v>1</v>
       </c>
       <c r="G292" t="n">
-        <v>856.5</v>
+        <v>1007</v>
       </c>
       <c r="H292" t="n">
         <v>1</v>
@@ -13899,16 +13899,16 @@
         <v>38567</v>
       </c>
       <c r="D293" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E293" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F293" t="n">
         <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>476.6666666666667</v>
+        <v>652.5</v>
       </c>
       <c r="H293" t="n">
         <v>1</v>
@@ -13920,10 +13920,10 @@
         <v>2</v>
       </c>
       <c r="K293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
         <v>2</v>
@@ -13954,7 +13954,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>520</v>
+        <v>817</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13991,16 +13991,16 @@
         <v>8429</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -14012,10 +14012,10 @@
         <v>1</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
         <v>1</v>
@@ -14037,16 +14037,16 @@
         <v>19608</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>451</v>
+        <v>372</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -14058,10 +14058,10 @@
         <v>4</v>
       </c>
       <c r="K296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>1</v>
@@ -14083,16 +14083,16 @@
         <v>26642</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E297" t="n">
         <v>1</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>681</v>
+        <v>468.5</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -14138,7 +14138,7 @@
         <v>2</v>
       </c>
       <c r="G298" t="n">
-        <v>380</v>
+        <v>522</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -14175,16 +14175,16 @@
         <v>9805</v>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E299" t="n">
         <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -14405,22 +14405,22 @@
         <v>16264</v>
       </c>
       <c r="D304" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>663</v>
+        <v>317.3333333333333</v>
       </c>
       <c r="H304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -14451,22 +14451,22 @@
         <v>14587</v>
       </c>
       <c r="D305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F305" t="n">
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>491</v>
+        <v>359</v>
       </c>
       <c r="H305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J305" t="n">
         <v>3</v>
@@ -14497,31 +14497,31 @@
         <v>31649</v>
       </c>
       <c r="D306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F306" t="n">
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J306" t="n">
         <v>6</v>
       </c>
       <c r="K306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M306" t="n">
         <v>1</v>
@@ -14552,7 +14552,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>858</v>
+        <v>1000</v>
       </c>
       <c r="H307" t="n">
         <v>1</v>
@@ -14819,16 +14819,16 @@
         <v>27752</v>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -14840,10 +14840,10 @@
         <v>1</v>
       </c>
       <c r="K313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>1</v>
@@ -14865,16 +14865,16 @@
         <v>21433</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E314" t="n">
         <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>957</v>
+        <v>638</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -15334,7 +15334,7 @@
         <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>519.5</v>
+        <v>557.25</v>
       </c>
       <c r="H324" t="n">
         <v>1</v>
@@ -15380,7 +15380,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="H325" t="n">
         <v>1</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="H330" t="n">
         <v>1</v>
@@ -15702,7 +15702,7 @@
         <v>1</v>
       </c>
       <c r="G332" t="n">
-        <v>194.6</v>
+        <v>232.6</v>
       </c>
       <c r="H332" t="n">
         <v>5</v>
@@ -15886,7 +15886,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="H336" t="n">
         <v>1</v>
@@ -15978,7 +15978,7 @@
         <v>2</v>
       </c>
       <c r="G338" t="n">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>896</v>
+        <v>952</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>813</v>
+        <v>868</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -16199,16 +16199,16 @@
         <v>13695</v>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E343" t="n">
         <v>1</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G343" t="n">
-        <v>615</v>
+        <v>359.5</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -16346,7 +16346,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>186.5</v>
+        <v>257.5</v>
       </c>
       <c r="H346" t="n">
         <v>2</v>
@@ -16392,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="G347" t="n">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -16438,7 +16438,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>197</v>
+        <v>290</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -16484,7 +16484,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="H349" t="n">
         <v>1</v>
@@ -16521,22 +16521,22 @@
         <v>9709</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>352</v>
+        <v>278</v>
       </c>
       <c r="H350" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350" t="n">
         <v>2</v>
@@ -16668,7 +16668,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>523</v>
+        <v>618</v>
       </c>
       <c r="H353" t="n">
         <v>1</v>
@@ -16797,16 +16797,16 @@
         <v>11184</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E356" t="n">
         <v>0</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -16843,16 +16843,16 @@
         <v>10248</v>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E357" t="n">
         <v>0</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -16889,16 +16889,16 @@
         <v>7102</v>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E358" t="n">
         <v>0</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G358" t="n">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -16981,16 +16981,16 @@
         <v>19755</v>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E360" t="n">
         <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -17027,16 +17027,16 @@
         <v>17657</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>2128</v>
+        <v>1194</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -17048,10 +17048,10 @@
         <v>1</v>
       </c>
       <c r="K361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M361" t="n">
         <v>2</v>
@@ -17082,7 +17082,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>308.5</v>
+        <v>421</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -17165,22 +17165,22 @@
         <v>17802</v>
       </c>
       <c r="D364" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F364" t="n">
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>407</v>
+        <v>379.3333333333333</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J364" t="n">
         <v>3</v>
@@ -17211,16 +17211,16 @@
         <v>8657</v>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E365" t="n">
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -17312,7 +17312,7 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>608</v>
+        <v>802</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -17358,7 +17358,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>715</v>
+        <v>795</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -17496,7 +17496,7 @@
         <v>2</v>
       </c>
       <c r="G371" t="n">
-        <v>180.6666666666667</v>
+        <v>260.3333333333333</v>
       </c>
       <c r="H371" t="n">
         <v>1</v>
@@ -17726,7 +17726,7 @@
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>719.3333333333334</v>
+        <v>854.3333333333334</v>
       </c>
       <c r="H376" t="n">
         <v>1</v>
@@ -17772,7 +17772,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>812</v>
+        <v>1009</v>
       </c>
       <c r="H377" t="n">
         <v>1</v>
@@ -17864,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="G379" t="n">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -17901,16 +17901,16 @@
         <v>20336</v>
       </c>
       <c r="D380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F380" t="n">
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -17922,10 +17922,10 @@
         <v>2</v>
       </c>
       <c r="K380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M380" t="n">
         <v>1</v>
@@ -17993,16 +17993,16 @@
         <v>22716</v>
       </c>
       <c r="D382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E382" t="n">
         <v>2</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
-        <v>215.6666666666667</v>
+        <v>253.75</v>
       </c>
       <c r="H382" t="n">
         <v>1</v>
@@ -18039,16 +18039,16 @@
         <v>25751</v>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E383" t="n">
         <v>1</v>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G383" t="n">
-        <v>135</v>
+        <v>148.6666666666667</v>
       </c>
       <c r="H383" t="n">
         <v>1</v>
@@ -18177,22 +18177,22 @@
         <v>30315</v>
       </c>
       <c r="D386" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E386" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F386" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G386" t="n">
-        <v>253.4285714285714</v>
+        <v>360.25</v>
       </c>
       <c r="H386" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I386" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J386" t="n">
         <v>7</v>
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>148</v>
+        <v>213.5</v>
       </c>
       <c r="H387" t="n">
         <v>2</v>
@@ -18269,16 +18269,16 @@
         <v>27530</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E388" t="n">
         <v>0</v>
       </c>
       <c r="F388" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G388" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -18324,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="G389" t="n">
-        <v>151.5</v>
+        <v>210.5</v>
       </c>
       <c r="H389" t="n">
         <v>1</v>
@@ -18407,16 +18407,16 @@
         <v>18586</v>
       </c>
       <c r="D391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G391" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -18428,10 +18428,10 @@
         <v>3</v>
       </c>
       <c r="K391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L391" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M391" t="n">
         <v>2</v>
@@ -18499,22 +18499,22 @@
         <v>8305</v>
       </c>
       <c r="D393" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F393" t="n">
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="H393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J393" t="n">
         <v>4</v>
@@ -18554,7 +18554,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="H394" t="n">
         <v>2</v>
